--- a/Result/profitability/6274.xlsx
+++ b/Result/profitability/6274.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.45625</v>
       </c>
       <c r="N2" t="n">
-        <v>22.12375</v>
+        <v>23.00125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>2.53125</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>21.4225</v>
+        <v>22.23875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>2.215</v>
+        <v>2.91375</v>
       </c>
       <c r="N4" t="n">
-        <v>19.81875</v>
+        <v>20.52625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8375</v>
+        <v>2.545</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6425</v>
+        <v>17.71125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>1.52125</v>
+        <v>2.07625</v>
       </c>
       <c r="N6" t="n">
-        <v>15.19625</v>
+        <v>15.9425</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.085</v>
+        <v>1.60625</v>
       </c>
       <c r="N7" t="n">
-        <v>14.14625</v>
+        <v>15.10125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0.63875</v>
+        <v>1.09625</v>
       </c>
       <c r="N8" t="n">
-        <v>13.4275</v>
+        <v>13.99875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.07625000000000023</v>
       </c>
       <c r="N9" t="n">
         <v>11.84</v>
@@ -1645,7 +1645,7 @@
         <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06</v>
+        <v>0.06000000000000023</v>
       </c>
       <c r="N10" t="n">
         <v>11.84625</v>
@@ -1772,7 +1772,7 @@
         <v>0.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07750000000000001</v>
+        <v>0.07750000000000024</v>
       </c>
       <c r="N11" t="n">
         <v>11.775</v>
@@ -1899,7 +1899,7 @@
         <v>0.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1225</v>
+        <v>0.1225000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>12.05</v>
@@ -2026,7 +2026,7 @@
         <v>0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2075</v>
+        <v>0.2075000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>13.41375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14301</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10051</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4250</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3358</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>69</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3427</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2342</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.9775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.659999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8394495412844034</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1817097415506959</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.398305084745763</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.549999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4038734057628719</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
